--- a/app/templates_excel/albedo/a7_angles_en.xlsx
+++ b/app/templates_excel/albedo/a7_angles_en.xlsx
@@ -1200,10 +1200,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>A window at an open grave.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>A bridge being built across a gorge.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1460,10 +1456,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Chinese woman nusing a baby with a message.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>One hand slightly flexed with a very prominent thumb.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1588,10 +1580,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>A pagent.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Sunshine just after a storm.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2352,10 +2340,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>A tree feiled and sawed.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Butterfly emerging from a chrysalis.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2432,10 +2416,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>A gigatic tent.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>A master instructing his pupil.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2456,10 +2436,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>An inhibited island.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>The purging of the priesthood.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2593,6 +2569,30 @@
   </si>
   <si>
     <t>A professor peering over his glasses.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A gigantic tent.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A tree felled and sawed.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chinese woman nursing a baby with a message.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A widow at an open grave.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A pageant.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>An inhabited island.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -10235,24 +10235,24 @@
         <v>3</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>723</v>
+        <v>717</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>724</v>
+        <v>718</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>703</v>
+        <v>697</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>704</v>
+        <v>698</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>348</v>
@@ -10260,7 +10260,7 @@
     </row>
     <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>705</v>
+        <v>699</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>349</v>
@@ -10492,18 +10492,18 @@
     </row>
     <row r="39" spans="1:6" s="7" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C39" s="7" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A40" s="8" t="s">
-        <v>706</v>
+        <v>700</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>378</v>
@@ -10511,7 +10511,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A41" s="8" t="s">
-        <v>707</v>
+        <v>701</v>
       </c>
       <c r="F41" s="6" t="s">
         <v>379</v>
@@ -10538,7 +10538,7 @@
         <v>34</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>382</v>
+        <v>728</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.4">
@@ -10546,7 +10546,7 @@
         <v>35</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.4">
@@ -10554,7 +10554,7 @@
         <v>36</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.4">
@@ -10562,7 +10562,7 @@
         <v>37</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.4">
@@ -10570,7 +10570,7 @@
         <v>38</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.4">
@@ -10578,7 +10578,7 @@
         <v>39</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.4">
@@ -10586,7 +10586,7 @@
         <v>40</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.4">
@@ -10594,7 +10594,7 @@
         <v>41</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.4">
@@ -10602,7 +10602,7 @@
         <v>42</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.4">
@@ -10610,7 +10610,7 @@
         <v>43</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.4">
@@ -10618,7 +10618,7 @@
         <v>44</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.4">
@@ -10626,7 +10626,7 @@
         <v>45</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.4">
@@ -10634,7 +10634,7 @@
         <v>46</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.4">
@@ -10642,7 +10642,7 @@
         <v>47</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.4">
@@ -10650,7 +10650,7 @@
         <v>48</v>
       </c>
       <c r="F58" s="6" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.4">
@@ -10658,7 +10658,7 @@
         <v>49</v>
       </c>
       <c r="F59" s="6" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.4">
@@ -10666,7 +10666,7 @@
         <v>50</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.4">
@@ -10674,7 +10674,7 @@
         <v>51</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.4">
@@ -10682,7 +10682,7 @@
         <v>52</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.4">
@@ -10690,7 +10690,7 @@
         <v>53</v>
       </c>
       <c r="F63" s="6" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.4">
@@ -10698,7 +10698,7 @@
         <v>54</v>
       </c>
       <c r="F64" s="6" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.4">
@@ -10706,7 +10706,7 @@
         <v>55</v>
       </c>
       <c r="F65" s="6" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.4">
@@ -10714,7 +10714,7 @@
         <v>56</v>
       </c>
       <c r="F66" s="6" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.4">
@@ -10722,7 +10722,7 @@
         <v>57</v>
       </c>
       <c r="F67" s="6" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.4">
@@ -10730,7 +10730,7 @@
         <v>58</v>
       </c>
       <c r="F68" s="6" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.4">
@@ -10738,37 +10738,37 @@
         <v>59</v>
       </c>
       <c r="F69" s="6" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="70" spans="1:6" s="7" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B70" s="7" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="E70" s="7" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A71" s="9" t="s">
-        <v>708</v>
+        <v>702</v>
       </c>
       <c r="F71" s="6" t="s">
-        <v>726</v>
+        <v>720</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A72" s="9" t="s">
-        <v>709</v>
+        <v>703</v>
       </c>
       <c r="F72" s="6" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.4">
@@ -10776,7 +10776,7 @@
         <v>60</v>
       </c>
       <c r="F73" s="6" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.4">
@@ -10784,7 +10784,7 @@
         <v>61</v>
       </c>
       <c r="F74" s="6" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.4">
@@ -10792,7 +10792,7 @@
         <v>62</v>
       </c>
       <c r="F75" s="6" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.4">
@@ -10800,7 +10800,7 @@
         <v>63</v>
       </c>
       <c r="F76" s="6" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.4">
@@ -10808,7 +10808,7 @@
         <v>64</v>
       </c>
       <c r="F77" s="6" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.4">
@@ -10816,7 +10816,7 @@
         <v>65</v>
       </c>
       <c r="F78" s="6" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.4">
@@ -10824,7 +10824,7 @@
         <v>66</v>
       </c>
       <c r="F79" s="6" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.4">
@@ -10832,7 +10832,7 @@
         <v>67</v>
       </c>
       <c r="F80" s="6" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.4">
@@ -10840,7 +10840,7 @@
         <v>68</v>
       </c>
       <c r="F81" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.4">
@@ -10848,7 +10848,7 @@
         <v>69</v>
       </c>
       <c r="F82" s="6" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.4">
@@ -10856,7 +10856,7 @@
         <v>70</v>
       </c>
       <c r="F83" s="6" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.4">
@@ -10864,7 +10864,7 @@
         <v>71</v>
       </c>
       <c r="F84" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.4">
@@ -10872,7 +10872,7 @@
         <v>72</v>
       </c>
       <c r="F85" s="6" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.4">
@@ -10880,7 +10880,7 @@
         <v>73</v>
       </c>
       <c r="F86" s="6" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.4">
@@ -10888,7 +10888,7 @@
         <v>74</v>
       </c>
       <c r="F87" s="6" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.4">
@@ -10896,7 +10896,7 @@
         <v>75</v>
       </c>
       <c r="F88" s="6" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.4">
@@ -10904,7 +10904,7 @@
         <v>76</v>
       </c>
       <c r="F89" s="6" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.4">
@@ -10912,7 +10912,7 @@
         <v>77</v>
       </c>
       <c r="F90" s="6" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.4">
@@ -10920,7 +10920,7 @@
         <v>78</v>
       </c>
       <c r="F91" s="6" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.4">
@@ -10928,7 +10928,7 @@
         <v>79</v>
       </c>
       <c r="F92" s="6" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.4">
@@ -10936,7 +10936,7 @@
         <v>80</v>
       </c>
       <c r="F93" s="6" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.4">
@@ -10944,7 +10944,7 @@
         <v>81</v>
       </c>
       <c r="F94" s="6" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.4">
@@ -10952,7 +10952,7 @@
         <v>82</v>
       </c>
       <c r="F95" s="6" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.4">
@@ -10960,7 +10960,7 @@
         <v>83</v>
       </c>
       <c r="F96" s="6" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.4">
@@ -10968,7 +10968,7 @@
         <v>84</v>
       </c>
       <c r="F97" s="6" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.4">
@@ -10976,7 +10976,7 @@
         <v>85</v>
       </c>
       <c r="F98" s="6" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.4">
@@ -10984,7 +10984,7 @@
         <v>86</v>
       </c>
       <c r="F99" s="6" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.4">
@@ -10992,29 +10992,29 @@
         <v>87</v>
       </c>
       <c r="F100" s="6" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="101" spans="1:6" s="7" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B101" s="7" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="D101" s="7" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="E101" s="7" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A102" s="10" t="s">
-        <v>710</v>
+        <v>704</v>
       </c>
       <c r="F102" s="6" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.4">
@@ -11022,7 +11022,7 @@
         <v>88</v>
       </c>
       <c r="F103" s="6" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.4">
@@ -11030,7 +11030,7 @@
         <v>89</v>
       </c>
       <c r="F104" s="6" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.4">
@@ -11038,7 +11038,7 @@
         <v>90</v>
       </c>
       <c r="F105" s="6" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.4">
@@ -11046,7 +11046,7 @@
         <v>91</v>
       </c>
       <c r="F106" s="6" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.4">
@@ -11054,7 +11054,7 @@
         <v>92</v>
       </c>
       <c r="F107" s="6" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.4">
@@ -11062,7 +11062,7 @@
         <v>93</v>
       </c>
       <c r="F108" s="6" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.4">
@@ -11070,7 +11070,7 @@
         <v>94</v>
       </c>
       <c r="F109" s="6" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.4">
@@ -11078,7 +11078,7 @@
         <v>95</v>
       </c>
       <c r="F110" s="6" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.4">
@@ -11086,7 +11086,7 @@
         <v>96</v>
       </c>
       <c r="F111" s="6" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.4">
@@ -11094,7 +11094,7 @@
         <v>97</v>
       </c>
       <c r="F112" s="6" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.4">
@@ -11102,7 +11102,7 @@
         <v>98</v>
       </c>
       <c r="F113" s="6" t="s">
-        <v>447</v>
+        <v>727</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.4">
@@ -11110,7 +11110,7 @@
         <v>99</v>
       </c>
       <c r="F114" s="6" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.4">
@@ -11118,7 +11118,7 @@
         <v>100</v>
       </c>
       <c r="F115" s="6" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.4">
@@ -11126,7 +11126,7 @@
         <v>101</v>
       </c>
       <c r="F116" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.4">
@@ -11134,7 +11134,7 @@
         <v>102</v>
       </c>
       <c r="F117" s="6" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.4">
@@ -11142,7 +11142,7 @@
         <v>103</v>
       </c>
       <c r="F118" s="6" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.4">
@@ -11150,7 +11150,7 @@
         <v>104</v>
       </c>
       <c r="F119" s="6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.4">
@@ -11158,7 +11158,7 @@
         <v>105</v>
       </c>
       <c r="F120" s="6" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.4">
@@ -11166,7 +11166,7 @@
         <v>106</v>
       </c>
       <c r="F121" s="6" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.4">
@@ -11174,7 +11174,7 @@
         <v>107</v>
       </c>
       <c r="F122" s="6" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.4">
@@ -11182,7 +11182,7 @@
         <v>108</v>
       </c>
       <c r="F123" s="6" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.4">
@@ -11190,7 +11190,7 @@
         <v>109</v>
       </c>
       <c r="F124" s="6" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.4">
@@ -11198,7 +11198,7 @@
         <v>110</v>
       </c>
       <c r="F125" s="6" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.4">
@@ -11206,7 +11206,7 @@
         <v>111</v>
       </c>
       <c r="F126" s="6" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.4">
@@ -11214,7 +11214,7 @@
         <v>112</v>
       </c>
       <c r="F127" s="6" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.4">
@@ -11222,7 +11222,7 @@
         <v>113</v>
       </c>
       <c r="F128" s="6" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.4">
@@ -11230,7 +11230,7 @@
         <v>114</v>
       </c>
       <c r="F129" s="6" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.4">
@@ -11238,7 +11238,7 @@
         <v>115</v>
       </c>
       <c r="F130" s="6" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.4">
@@ -11246,29 +11246,29 @@
         <v>116</v>
       </c>
       <c r="F131" s="6" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="132" spans="1:6" s="7" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B132" s="7" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="C132" s="7" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="D132" s="7" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="E132" s="7" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A133" s="5" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="F133" s="6" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.4">
@@ -11276,7 +11276,7 @@
         <v>117</v>
       </c>
       <c r="F134" s="6" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.4">
@@ -11284,7 +11284,7 @@
         <v>118</v>
       </c>
       <c r="F135" s="6" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.4">
@@ -11292,7 +11292,7 @@
         <v>119</v>
       </c>
       <c r="F136" s="6" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.4">
@@ -11300,7 +11300,7 @@
         <v>120</v>
       </c>
       <c r="F137" s="6" t="s">
-        <v>729</v>
+        <v>723</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.4">
@@ -11308,7 +11308,7 @@
         <v>121</v>
       </c>
       <c r="F138" s="6" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.4">
@@ -11316,7 +11316,7 @@
         <v>122</v>
       </c>
       <c r="F139" s="6" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.4">
@@ -11324,7 +11324,7 @@
         <v>123</v>
       </c>
       <c r="F140" s="6" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.4">
@@ -11332,7 +11332,7 @@
         <v>124</v>
       </c>
       <c r="F141" s="6" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.4">
@@ -11340,7 +11340,7 @@
         <v>125</v>
       </c>
       <c r="F142" s="6" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.4">
@@ -11348,7 +11348,7 @@
         <v>126</v>
       </c>
       <c r="F143" s="6" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.4">
@@ -11356,7 +11356,7 @@
         <v>127</v>
       </c>
       <c r="F144" s="6" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.4">
@@ -11364,7 +11364,7 @@
         <v>128</v>
       </c>
       <c r="F145" s="6" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.4">
@@ -11372,7 +11372,7 @@
         <v>129</v>
       </c>
       <c r="F146" s="6" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.4">
@@ -11380,7 +11380,7 @@
         <v>130</v>
       </c>
       <c r="F147" s="6" t="s">
-        <v>479</v>
+        <v>729</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.4">
@@ -11388,7 +11388,7 @@
         <v>131</v>
       </c>
       <c r="F148" s="6" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.4">
@@ -11396,7 +11396,7 @@
         <v>132</v>
       </c>
       <c r="F149" s="6" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.4">
@@ -11404,7 +11404,7 @@
         <v>133</v>
       </c>
       <c r="F150" s="6" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.4">
@@ -11412,7 +11412,7 @@
         <v>134</v>
       </c>
       <c r="F151" s="6" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.4">
@@ -11420,7 +11420,7 @@
         <v>135</v>
       </c>
       <c r="F152" s="6" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.4">
@@ -11428,7 +11428,7 @@
         <v>136</v>
       </c>
       <c r="F153" s="6" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.4">
@@ -11436,7 +11436,7 @@
         <v>137</v>
       </c>
       <c r="F154" s="6" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.4">
@@ -11444,7 +11444,7 @@
         <v>138</v>
       </c>
       <c r="F155" s="6" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.4">
@@ -11452,7 +11452,7 @@
         <v>139</v>
       </c>
       <c r="F156" s="6" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.4">
@@ -11460,7 +11460,7 @@
         <v>140</v>
       </c>
       <c r="F157" s="6" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.4">
@@ -11468,7 +11468,7 @@
         <v>141</v>
       </c>
       <c r="F158" s="6" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.4">
@@ -11476,7 +11476,7 @@
         <v>142</v>
       </c>
       <c r="F159" s="6" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.4">
@@ -11484,7 +11484,7 @@
         <v>143</v>
       </c>
       <c r="F160" s="6" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.4">
@@ -11492,7 +11492,7 @@
         <v>144</v>
       </c>
       <c r="F161" s="6" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.4">
@@ -11500,37 +11500,37 @@
         <v>145</v>
       </c>
       <c r="F162" s="6" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
     </row>
     <row r="163" spans="1:6" s="7" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B163" s="7" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="C163" s="7" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="D163" s="7" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="E163" s="7" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A164" s="8" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="F164" s="6" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A165" s="8" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="F165" s="6" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.4">
@@ -11538,7 +11538,7 @@
         <v>146</v>
       </c>
       <c r="F166" s="6" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.4">
@@ -11546,7 +11546,7 @@
         <v>147</v>
       </c>
       <c r="F167" s="6" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.4">
@@ -11554,7 +11554,7 @@
         <v>148</v>
       </c>
       <c r="F168" s="6" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.4">
@@ -11562,7 +11562,7 @@
         <v>149</v>
       </c>
       <c r="F169" s="6" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.4">
@@ -11570,7 +11570,7 @@
         <v>150</v>
       </c>
       <c r="F170" s="6" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.4">
@@ -11578,7 +11578,7 @@
         <v>151</v>
       </c>
       <c r="F171" s="6" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.4">
@@ -11586,7 +11586,7 @@
         <v>152</v>
       </c>
       <c r="F172" s="6" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.4">
@@ -11594,7 +11594,7 @@
         <v>153</v>
       </c>
       <c r="F173" s="6" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.4">
@@ -11602,7 +11602,7 @@
         <v>154</v>
       </c>
       <c r="F174" s="6" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.4">
@@ -11610,7 +11610,7 @@
         <v>155</v>
       </c>
       <c r="F175" s="6" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.4">
@@ -11618,7 +11618,7 @@
         <v>156</v>
       </c>
       <c r="F176" s="6" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.4">
@@ -11626,7 +11626,7 @@
         <v>157</v>
       </c>
       <c r="F177" s="6" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.4">
@@ -11634,7 +11634,7 @@
         <v>158</v>
       </c>
       <c r="F178" s="6" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.4">
@@ -11642,7 +11642,7 @@
         <v>159</v>
       </c>
       <c r="F179" s="6" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.4">
@@ -11650,7 +11650,7 @@
         <v>160</v>
       </c>
       <c r="F180" s="6" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.4">
@@ -11658,7 +11658,7 @@
         <v>161</v>
       </c>
       <c r="F181" s="6" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.4">
@@ -11666,7 +11666,7 @@
         <v>162</v>
       </c>
       <c r="F182" s="6" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.4">
@@ -11674,7 +11674,7 @@
         <v>163</v>
       </c>
       <c r="F183" s="6" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.4">
@@ -11682,7 +11682,7 @@
         <v>164</v>
       </c>
       <c r="F184" s="6" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.4">
@@ -11690,7 +11690,7 @@
         <v>165</v>
       </c>
       <c r="F185" s="6" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.4">
@@ -11698,7 +11698,7 @@
         <v>166</v>
       </c>
       <c r="F186" s="6" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.4">
@@ -11706,7 +11706,7 @@
         <v>167</v>
       </c>
       <c r="F187" s="6" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.4">
@@ -11714,7 +11714,7 @@
         <v>168</v>
       </c>
       <c r="F188" s="6" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.4">
@@ -11722,7 +11722,7 @@
         <v>169</v>
       </c>
       <c r="F189" s="6" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.4">
@@ -11730,7 +11730,7 @@
         <v>170</v>
       </c>
       <c r="F190" s="6" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.4">
@@ -11738,7 +11738,7 @@
         <v>171</v>
       </c>
       <c r="F191" s="6" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.4">
@@ -11746,7 +11746,7 @@
         <v>172</v>
       </c>
       <c r="F192" s="6" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.4">
@@ -11754,29 +11754,29 @@
         <v>173</v>
       </c>
       <c r="F193" s="6" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
     </row>
     <row r="194" spans="1:6" s="7" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B194" s="7" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="C194" s="7" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="D194" s="7" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="E194" s="7" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A195" s="9" t="s">
-        <v>714</v>
+        <v>708</v>
       </c>
       <c r="F195" s="6" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.4">
@@ -11784,7 +11784,7 @@
         <v>174</v>
       </c>
       <c r="F196" s="6" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.4">
@@ -11792,7 +11792,7 @@
         <v>175</v>
       </c>
       <c r="F197" s="6" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.4">
@@ -11800,7 +11800,7 @@
         <v>176</v>
       </c>
       <c r="F198" s="6" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.4">
@@ -11808,7 +11808,7 @@
         <v>177</v>
       </c>
       <c r="F199" s="6" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.4">
@@ -11816,7 +11816,7 @@
         <v>178</v>
       </c>
       <c r="F200" s="6" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.4">
@@ -11824,7 +11824,7 @@
         <v>179</v>
       </c>
       <c r="F201" s="6" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.4">
@@ -11832,7 +11832,7 @@
         <v>180</v>
       </c>
       <c r="F202" s="6" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.4">
@@ -11840,7 +11840,7 @@
         <v>181</v>
       </c>
       <c r="F203" s="6" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.4">
@@ -11848,7 +11848,7 @@
         <v>182</v>
       </c>
       <c r="F204" s="6" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.4">
@@ -11856,7 +11856,7 @@
         <v>183</v>
       </c>
       <c r="F205" s="6" t="s">
-        <v>730</v>
+        <v>724</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.4">
@@ -11864,7 +11864,7 @@
         <v>184</v>
       </c>
       <c r="F206" s="6" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.4">
@@ -11872,7 +11872,7 @@
         <v>185</v>
       </c>
       <c r="F207" s="6" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.4">
@@ -11880,7 +11880,7 @@
         <v>186</v>
       </c>
       <c r="F208" s="6" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.4">
@@ -11888,7 +11888,7 @@
         <v>187</v>
       </c>
       <c r="F209" s="6" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.4">
@@ -11896,7 +11896,7 @@
         <v>188</v>
       </c>
       <c r="F210" s="6" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.4">
@@ -11904,7 +11904,7 @@
         <v>189</v>
       </c>
       <c r="F211" s="6" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.4">
@@ -11912,7 +11912,7 @@
         <v>190</v>
       </c>
       <c r="F212" s="6" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.4">
@@ -11920,7 +11920,7 @@
         <v>191</v>
       </c>
       <c r="F213" s="6" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.4">
@@ -11928,7 +11928,7 @@
         <v>192</v>
       </c>
       <c r="F214" s="6" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.4">
@@ -11936,7 +11936,7 @@
         <v>193</v>
       </c>
       <c r="F215" s="6" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.4">
@@ -11944,7 +11944,7 @@
         <v>194</v>
       </c>
       <c r="F216" s="6" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.4">
@@ -11952,7 +11952,7 @@
         <v>195</v>
       </c>
       <c r="F217" s="6" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.4">
@@ -11960,7 +11960,7 @@
         <v>196</v>
       </c>
       <c r="F218" s="6" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.4">
@@ -11968,7 +11968,7 @@
         <v>197</v>
       </c>
       <c r="F219" s="6" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.4">
@@ -11976,7 +11976,7 @@
         <v>198</v>
       </c>
       <c r="F220" s="6" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.4">
@@ -11984,7 +11984,7 @@
         <v>199</v>
       </c>
       <c r="F221" s="6" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.4">
@@ -11992,7 +11992,7 @@
         <v>200</v>
       </c>
       <c r="F222" s="6" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.4">
@@ -12000,7 +12000,7 @@
         <v>201</v>
       </c>
       <c r="F223" s="6" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.4">
@@ -12008,29 +12008,29 @@
         <v>202</v>
       </c>
       <c r="F224" s="6" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
     </row>
     <row r="225" spans="1:6" s="7" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B225" s="7" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="C225" s="7" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="D225" s="7" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="E225" s="7" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A226" s="10" t="s">
-        <v>715</v>
+        <v>709</v>
       </c>
       <c r="F226" s="6" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.4">
@@ -12038,7 +12038,7 @@
         <v>203</v>
       </c>
       <c r="F227" s="6" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.4">
@@ -12046,7 +12046,7 @@
         <v>204</v>
       </c>
       <c r="F228" s="6" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.4">
@@ -12054,7 +12054,7 @@
         <v>205</v>
       </c>
       <c r="F229" s="6" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.4">
@@ -12062,7 +12062,7 @@
         <v>206</v>
       </c>
       <c r="F230" s="6" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.4">
@@ -12070,7 +12070,7 @@
         <v>207</v>
       </c>
       <c r="F231" s="6" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.4">
@@ -12078,7 +12078,7 @@
         <v>208</v>
       </c>
       <c r="F232" s="6" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.4">
@@ -12086,7 +12086,7 @@
         <v>209</v>
       </c>
       <c r="F233" s="6" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.4">
@@ -12094,7 +12094,7 @@
         <v>210</v>
       </c>
       <c r="F234" s="6" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.4">
@@ -12102,7 +12102,7 @@
         <v>211</v>
       </c>
       <c r="F235" s="6" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.4">
@@ -12110,7 +12110,7 @@
         <v>212</v>
       </c>
       <c r="F236" s="6" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.4">
@@ -12118,7 +12118,7 @@
         <v>213</v>
       </c>
       <c r="F237" s="6" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.4">
@@ -12126,7 +12126,7 @@
         <v>214</v>
       </c>
       <c r="F238" s="6" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.4">
@@ -12134,7 +12134,7 @@
         <v>215</v>
       </c>
       <c r="F239" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.4">
@@ -12142,7 +12142,7 @@
         <v>216</v>
       </c>
       <c r="F240" s="6" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.4">
@@ -12150,7 +12150,7 @@
         <v>217</v>
       </c>
       <c r="F241" s="6" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.4">
@@ -12158,7 +12158,7 @@
         <v>218</v>
       </c>
       <c r="F242" s="6" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.4">
@@ -12166,7 +12166,7 @@
         <v>219</v>
       </c>
       <c r="F243" s="6" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.4">
@@ -12174,7 +12174,7 @@
         <v>220</v>
       </c>
       <c r="F244" s="6" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.4">
@@ -12182,7 +12182,7 @@
         <v>221</v>
       </c>
       <c r="F245" s="6" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.4">
@@ -12190,7 +12190,7 @@
         <v>222</v>
       </c>
       <c r="F246" s="6" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.4">
@@ -12198,7 +12198,7 @@
         <v>223</v>
       </c>
       <c r="F247" s="6" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.4">
@@ -12206,7 +12206,7 @@
         <v>224</v>
       </c>
       <c r="F248" s="6" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.4">
@@ -12214,7 +12214,7 @@
         <v>225</v>
       </c>
       <c r="F249" s="6" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.4">
@@ -12222,7 +12222,7 @@
         <v>226</v>
       </c>
       <c r="F250" s="6" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.4">
@@ -12230,7 +12230,7 @@
         <v>227</v>
       </c>
       <c r="F251" s="6" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.4">
@@ -12238,7 +12238,7 @@
         <v>228</v>
       </c>
       <c r="F252" s="6" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.4">
@@ -12246,7 +12246,7 @@
         <v>229</v>
       </c>
       <c r="F253" s="6" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.4">
@@ -12254,7 +12254,7 @@
         <v>230</v>
       </c>
       <c r="F254" s="6" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.4">
@@ -12262,29 +12262,29 @@
         <v>231</v>
       </c>
       <c r="F255" s="6" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
     </row>
     <row r="256" spans="1:6" s="7" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B256" s="7" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="C256" s="7" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="D256" s="7" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="E256" s="7" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A257" s="5" t="s">
-        <v>716</v>
+        <v>710</v>
       </c>
       <c r="F257" s="6" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.4">
@@ -12292,7 +12292,7 @@
         <v>232</v>
       </c>
       <c r="F258" s="6" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.4">
@@ -12300,7 +12300,7 @@
         <v>233</v>
       </c>
       <c r="F259" s="6" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.4">
@@ -12308,7 +12308,7 @@
         <v>234</v>
       </c>
       <c r="F260" s="6" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.4">
@@ -12316,7 +12316,7 @@
         <v>235</v>
       </c>
       <c r="F261" s="6" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.4">
@@ -12324,7 +12324,7 @@
         <v>236</v>
       </c>
       <c r="F262" s="6" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.4">
@@ -12332,7 +12332,7 @@
         <v>237</v>
       </c>
       <c r="F263" s="6" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.4">
@@ -12340,7 +12340,7 @@
         <v>238</v>
       </c>
       <c r="F264" s="6" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.4">
@@ -12348,7 +12348,7 @@
         <v>239</v>
       </c>
       <c r="F265" s="6" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.4">
@@ -12356,7 +12356,7 @@
         <v>240</v>
       </c>
       <c r="F266" s="6" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.4">
@@ -12364,7 +12364,7 @@
         <v>241</v>
       </c>
       <c r="F267" s="6" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.4">
@@ -12372,7 +12372,7 @@
         <v>242</v>
       </c>
       <c r="F268" s="6" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.4">
@@ -12380,7 +12380,7 @@
         <v>243</v>
       </c>
       <c r="F269" s="6" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.4">
@@ -12388,7 +12388,7 @@
         <v>244</v>
       </c>
       <c r="F270" s="6" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.4">
@@ -12396,7 +12396,7 @@
         <v>245</v>
       </c>
       <c r="F271" s="6" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.4">
@@ -12404,7 +12404,7 @@
         <v>246</v>
       </c>
       <c r="F272" s="6" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.4">
@@ -12412,7 +12412,7 @@
         <v>247</v>
       </c>
       <c r="F273" s="6" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.4">
@@ -12420,7 +12420,7 @@
         <v>248</v>
       </c>
       <c r="F274" s="6" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.4">
@@ -12428,7 +12428,7 @@
         <v>249</v>
       </c>
       <c r="F275" s="6" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.4">
@@ -12436,7 +12436,7 @@
         <v>250</v>
       </c>
       <c r="F276" s="6" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.4">
@@ -12444,7 +12444,7 @@
         <v>251</v>
       </c>
       <c r="F277" s="6" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.4">
@@ -12452,7 +12452,7 @@
         <v>252</v>
       </c>
       <c r="F278" s="6" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.4">
@@ -12460,7 +12460,7 @@
         <v>253</v>
       </c>
       <c r="F279" s="6" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.4">
@@ -12468,7 +12468,7 @@
         <v>254</v>
       </c>
       <c r="F280" s="6" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.4">
@@ -12476,7 +12476,7 @@
         <v>255</v>
       </c>
       <c r="F281" s="6" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.4">
@@ -12484,7 +12484,7 @@
         <v>256</v>
       </c>
       <c r="F282" s="6" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.4">
@@ -12492,7 +12492,7 @@
         <v>257</v>
       </c>
       <c r="F283" s="6" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.4">
@@ -12500,7 +12500,7 @@
         <v>258</v>
       </c>
       <c r="F284" s="6" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.4">
@@ -12508,7 +12508,7 @@
         <v>259</v>
       </c>
       <c r="F285" s="6" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.4">
@@ -12516,29 +12516,29 @@
         <v>260</v>
       </c>
       <c r="F286" s="6" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="287" spans="1:6" s="7" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B287" s="7" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="C287" s="7" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="D287" s="7" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="E287" s="7" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A288" s="8" t="s">
-        <v>717</v>
+        <v>711</v>
       </c>
       <c r="F288" s="6" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.4">
@@ -12546,7 +12546,7 @@
         <v>261</v>
       </c>
       <c r="F289" s="6" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.4">
@@ -12554,7 +12554,7 @@
         <v>262</v>
       </c>
       <c r="F290" s="6" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.4">
@@ -12562,7 +12562,7 @@
         <v>263</v>
       </c>
       <c r="F291" s="6" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.4">
@@ -12570,7 +12570,7 @@
         <v>264</v>
       </c>
       <c r="F292" s="6" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.4">
@@ -12578,7 +12578,7 @@
         <v>265</v>
       </c>
       <c r="F293" s="6" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.4">
@@ -12586,7 +12586,7 @@
         <v>266</v>
       </c>
       <c r="F294" s="6" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.4">
@@ -12594,7 +12594,7 @@
         <v>267</v>
       </c>
       <c r="F295" s="6" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.4">
@@ -12602,7 +12602,7 @@
         <v>268</v>
       </c>
       <c r="F296" s="6" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.4">
@@ -12610,7 +12610,7 @@
         <v>269</v>
       </c>
       <c r="F297" s="6" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.4">
@@ -12618,7 +12618,7 @@
         <v>270</v>
       </c>
       <c r="F298" s="6" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.4">
@@ -12626,7 +12626,7 @@
         <v>271</v>
       </c>
       <c r="F299" s="6" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.4">
@@ -12634,7 +12634,7 @@
         <v>272</v>
       </c>
       <c r="F300" s="6" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.4">
@@ -12642,7 +12642,7 @@
         <v>273</v>
       </c>
       <c r="F301" s="6" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.4">
@@ -12650,7 +12650,7 @@
         <v>274</v>
       </c>
       <c r="F302" s="6" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.4">
@@ -12658,7 +12658,7 @@
         <v>275</v>
       </c>
       <c r="F303" s="6" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.4">
@@ -12666,7 +12666,7 @@
         <v>276</v>
       </c>
       <c r="F304" s="6" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.4">
@@ -12674,7 +12674,7 @@
         <v>277</v>
       </c>
       <c r="F305" s="6" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.4">
@@ -12682,7 +12682,7 @@
         <v>278</v>
       </c>
       <c r="F306" s="6" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.4">
@@ -12690,7 +12690,7 @@
         <v>279</v>
       </c>
       <c r="F307" s="6" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.4">
@@ -12698,7 +12698,7 @@
         <v>280</v>
       </c>
       <c r="F308" s="6" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.4">
@@ -12706,7 +12706,7 @@
         <v>281</v>
       </c>
       <c r="F309" s="6" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.4">
@@ -12714,7 +12714,7 @@
         <v>282</v>
       </c>
       <c r="F310" s="6" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.4">
@@ -12722,7 +12722,7 @@
         <v>283</v>
       </c>
       <c r="F311" s="6" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.4">
@@ -12730,7 +12730,7 @@
         <v>284</v>
       </c>
       <c r="F312" s="6" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.4">
@@ -12738,7 +12738,7 @@
         <v>285</v>
       </c>
       <c r="F313" s="6" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.4">
@@ -12746,7 +12746,7 @@
         <v>286</v>
       </c>
       <c r="F314" s="6" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.4">
@@ -12754,7 +12754,7 @@
         <v>287</v>
       </c>
       <c r="F315" s="6" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.4">
@@ -12762,7 +12762,7 @@
         <v>288</v>
       </c>
       <c r="F316" s="6" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.4">
@@ -12770,29 +12770,29 @@
         <v>289</v>
       </c>
       <c r="F317" s="6" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
     </row>
     <row r="318" spans="1:6" s="7" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B318" s="7" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="C318" s="7" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="D318" s="7" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="E318" s="7" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A319" s="9" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="F319" s="6" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.4">
@@ -12800,7 +12800,7 @@
         <v>290</v>
       </c>
       <c r="F320" s="6" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.4">
@@ -12808,7 +12808,7 @@
         <v>291</v>
       </c>
       <c r="F321" s="6" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.4">
@@ -12816,7 +12816,7 @@
         <v>292</v>
       </c>
       <c r="F322" s="6" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.4">
@@ -12824,7 +12824,7 @@
         <v>293</v>
       </c>
       <c r="F323" s="6" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.4">
@@ -12832,7 +12832,7 @@
         <v>294</v>
       </c>
       <c r="F324" s="6" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.4">
@@ -12840,7 +12840,7 @@
         <v>295</v>
       </c>
       <c r="F325" s="6" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.4">
@@ -12848,7 +12848,7 @@
         <v>296</v>
       </c>
       <c r="F326" s="6" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.4">
@@ -12856,7 +12856,7 @@
         <v>297</v>
       </c>
       <c r="F327" s="6" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.4">
@@ -12864,7 +12864,7 @@
         <v>298</v>
       </c>
       <c r="F328" s="6" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.4">
@@ -12872,7 +12872,7 @@
         <v>299</v>
       </c>
       <c r="F329" s="6" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.4">
@@ -12880,7 +12880,7 @@
         <v>300</v>
       </c>
       <c r="F330" s="6" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.4">
@@ -12888,7 +12888,7 @@
         <v>301</v>
       </c>
       <c r="F331" s="6" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.4">
@@ -12896,7 +12896,7 @@
         <v>302</v>
       </c>
       <c r="F332" s="6" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.4">
@@ -12904,7 +12904,7 @@
         <v>303</v>
       </c>
       <c r="F333" s="6" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.4">
@@ -12912,7 +12912,7 @@
         <v>304</v>
       </c>
       <c r="F334" s="6" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.4">
@@ -12920,7 +12920,7 @@
         <v>305</v>
       </c>
       <c r="F335" s="6" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.4">
@@ -12928,7 +12928,7 @@
         <v>306</v>
       </c>
       <c r="F336" s="6" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.4">
@@ -12936,7 +12936,7 @@
         <v>307</v>
       </c>
       <c r="F337" s="6" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.4">
@@ -12944,7 +12944,7 @@
         <v>308</v>
       </c>
       <c r="F338" s="6" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.4">
@@ -12952,7 +12952,7 @@
         <v>309</v>
       </c>
       <c r="F339" s="6" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.4">
@@ -12960,7 +12960,7 @@
         <v>310</v>
       </c>
       <c r="F340" s="6" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.4">
@@ -12968,7 +12968,7 @@
         <v>311</v>
       </c>
       <c r="F341" s="6" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.4">
@@ -12976,7 +12976,7 @@
         <v>312</v>
       </c>
       <c r="F342" s="6" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.4">
@@ -12984,7 +12984,7 @@
         <v>313</v>
       </c>
       <c r="F343" s="6" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.4">
@@ -12992,7 +12992,7 @@
         <v>314</v>
       </c>
       <c r="F344" s="6" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.4">
@@ -13000,7 +13000,7 @@
         <v>315</v>
       </c>
       <c r="F345" s="6" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.4">
@@ -13008,7 +13008,7 @@
         <v>316</v>
       </c>
       <c r="F346" s="6" t="s">
-        <v>670</v>
+        <v>726</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.4">
@@ -13016,7 +13016,7 @@
         <v>317</v>
       </c>
       <c r="F347" s="6" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.4">
@@ -13024,29 +13024,29 @@
         <v>318</v>
       </c>
       <c r="F348" s="6" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
     </row>
     <row r="349" spans="1:6" s="7" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B349" s="7" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="C349" s="7" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="D349" s="7" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="E349" s="7" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A350" s="10" t="s">
-        <v>719</v>
+        <v>713</v>
       </c>
       <c r="F350" s="6" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.4">
@@ -13054,7 +13054,7 @@
         <v>319</v>
       </c>
       <c r="F351" s="6" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.4">
@@ -13062,7 +13062,7 @@
         <v>320</v>
       </c>
       <c r="F352" s="6" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.4">
@@ -13070,7 +13070,7 @@
         <v>321</v>
       </c>
       <c r="F353" s="6" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.4">
@@ -13078,7 +13078,7 @@
         <v>322</v>
       </c>
       <c r="F354" s="6" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.4">
@@ -13086,7 +13086,7 @@
         <v>323</v>
       </c>
       <c r="F355" s="6" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.4">
@@ -13094,7 +13094,7 @@
         <v>324</v>
       </c>
       <c r="F356" s="6" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
     </row>
     <row r="357" spans="1:6" x14ac:dyDescent="0.4">
@@ -13102,7 +13102,7 @@
         <v>325</v>
       </c>
       <c r="F357" s="6" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
     </row>
     <row r="358" spans="1:6" x14ac:dyDescent="0.4">
@@ -13110,7 +13110,7 @@
         <v>326</v>
       </c>
       <c r="F358" s="6" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
     </row>
     <row r="359" spans="1:6" x14ac:dyDescent="0.4">
@@ -13118,7 +13118,7 @@
         <v>327</v>
       </c>
       <c r="F359" s="6" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
     </row>
     <row r="360" spans="1:6" x14ac:dyDescent="0.4">
@@ -13126,7 +13126,7 @@
         <v>328</v>
       </c>
       <c r="F360" s="6" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
     </row>
     <row r="361" spans="1:6" x14ac:dyDescent="0.4">
@@ -13134,7 +13134,7 @@
         <v>329</v>
       </c>
       <c r="F361" s="6" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
     </row>
     <row r="362" spans="1:6" x14ac:dyDescent="0.4">
@@ -13142,7 +13142,7 @@
         <v>330</v>
       </c>
       <c r="F362" s="6" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
     </row>
     <row r="363" spans="1:6" x14ac:dyDescent="0.4">
@@ -13150,7 +13150,7 @@
         <v>331</v>
       </c>
       <c r="F363" s="6" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.4">
@@ -13158,7 +13158,7 @@
         <v>332</v>
       </c>
       <c r="F364" s="6" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.4">
@@ -13166,7 +13166,7 @@
         <v>333</v>
       </c>
       <c r="F365" s="6" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.4">
@@ -13174,7 +13174,7 @@
         <v>334</v>
       </c>
       <c r="F366" s="6" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.4">
@@ -13182,7 +13182,7 @@
         <v>335</v>
       </c>
       <c r="F367" s="6" t="s">
-        <v>690</v>
+        <v>725</v>
       </c>
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.4">
@@ -13190,7 +13190,7 @@
         <v>336</v>
       </c>
       <c r="F368" s="6" t="s">
-        <v>691</v>
+        <v>686</v>
       </c>
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.4">
@@ -13198,7 +13198,7 @@
         <v>337</v>
       </c>
       <c r="F369" s="6" t="s">
-        <v>692</v>
+        <v>687</v>
       </c>
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.4">
@@ -13206,7 +13206,7 @@
         <v>338</v>
       </c>
       <c r="F370" s="6" t="s">
-        <v>693</v>
+        <v>688</v>
       </c>
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.4">
@@ -13214,7 +13214,7 @@
         <v>339</v>
       </c>
       <c r="F371" s="6" t="s">
-        <v>694</v>
+        <v>689</v>
       </c>
     </row>
     <row r="372" spans="1:6" x14ac:dyDescent="0.4">
@@ -13222,7 +13222,7 @@
         <v>340</v>
       </c>
       <c r="F372" s="6" t="s">
-        <v>695</v>
+        <v>690</v>
       </c>
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.4">
@@ -13230,7 +13230,7 @@
         <v>341</v>
       </c>
       <c r="F373" s="6" t="s">
-        <v>696</v>
+        <v>730</v>
       </c>
     </row>
     <row r="374" spans="1:6" x14ac:dyDescent="0.4">
@@ -13238,7 +13238,7 @@
         <v>342</v>
       </c>
       <c r="F374" s="6" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.4">
@@ -13246,7 +13246,7 @@
         <v>343</v>
       </c>
       <c r="F375" s="6" t="s">
-        <v>698</v>
+        <v>692</v>
       </c>
     </row>
     <row r="376" spans="1:6" x14ac:dyDescent="0.4">
@@ -13254,7 +13254,7 @@
         <v>344</v>
       </c>
       <c r="F376" s="6" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
     </row>
     <row r="377" spans="1:6" x14ac:dyDescent="0.4">
@@ -13262,7 +13262,7 @@
         <v>345</v>
       </c>
       <c r="F377" s="6" t="s">
-        <v>700</v>
+        <v>694</v>
       </c>
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.4">
@@ -13270,7 +13270,7 @@
         <v>346</v>
       </c>
       <c r="F378" s="6" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.4">
@@ -13278,27 +13278,27 @@
         <v>347</v>
       </c>
       <c r="F379" s="6" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
     </row>
     <row r="380" spans="1:6" s="7" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A380" s="7" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="B380" s="7" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="C380" s="7" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="D380" s="7" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="E380" s="7" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="F380" s="7" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
     </row>
   </sheetData>
